--- a/sgturnos/mallas/malla_ter04_2026-01.xlsx
+++ b/sgturnos/mallas/malla_ter04_2026-01.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="340" uniqueCount="51">
   <si>
     <t>Empleado</t>
   </si>
@@ -125,15 +125,18 @@
     <t>CP3h+AP9h</t>
   </si>
   <si>
+    <t>AP12h</t>
+  </si>
+  <si>
+    <t>TN</t>
+  </si>
+  <si>
+    <t>PT</t>
+  </si>
+  <si>
     <t>LB</t>
   </si>
   <si>
-    <t>TN</t>
-  </si>
-  <si>
-    <t>PT</t>
-  </si>
-  <si>
     <t>16</t>
   </si>
   <si>
@@ -150,6 +153,9 @@
   </si>
   <si>
     <t>Esteban Salinas</t>
+  </si>
+  <si>
+    <t>Leonardo Dicaprio</t>
   </si>
   <si>
     <t>Angelica Prada</t>
@@ -269,7 +275,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AH9"/>
+  <dimension ref="A1:AH10"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -389,7 +395,7 @@
       <c r="D2" t="s" s="1">
         <v>35</v>
       </c>
-      <c r="E2" t="s" s="4">
+      <c r="E2" t="s" s="3">
         <v>37</v>
       </c>
       <c r="F2" t="s" s="2">
@@ -398,53 +404,53 @@
       <c r="G2" t="s" s="5">
         <v>39</v>
       </c>
-      <c r="H2" t="s" s="1">
-        <v>35</v>
-      </c>
-      <c r="I2" t="s" s="4">
-        <v>37</v>
-      </c>
-      <c r="J2" t="s" s="1">
-        <v>35</v>
-      </c>
-      <c r="K2" t="s" s="4">
-        <v>37</v>
-      </c>
-      <c r="L2" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="M2" t="s" s="5">
-        <v>39</v>
-      </c>
-      <c r="N2" t="s" s="1">
-        <v>35</v>
-      </c>
-      <c r="O2" t="s" s="4">
-        <v>37</v>
-      </c>
-      <c r="P2" t="s" s="1">
-        <v>35</v>
-      </c>
-      <c r="Q2" t="s" s="4">
-        <v>37</v>
-      </c>
-      <c r="R2" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="S2" t="s" s="5">
-        <v>39</v>
+      <c r="H2" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="I2" t="s" s="5">
+        <v>39</v>
+      </c>
+      <c r="J2" t="s" s="4">
+        <v>40</v>
+      </c>
+      <c r="K2" t="s" s="1">
+        <v>35</v>
+      </c>
+      <c r="L2" t="s" s="4">
+        <v>40</v>
+      </c>
+      <c r="M2" t="s" s="1">
+        <v>35</v>
+      </c>
+      <c r="N2" t="s" s="4">
+        <v>40</v>
+      </c>
+      <c r="O2" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="P2" t="s" s="5">
+        <v>39</v>
+      </c>
+      <c r="Q2" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="R2" t="s" s="5">
+        <v>39</v>
+      </c>
+      <c r="S2" t="s" s="4">
+        <v>40</v>
       </c>
       <c r="T2" t="s" s="1">
         <v>35</v>
       </c>
       <c r="U2" t="s" s="4">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="V2" t="s" s="1">
         <v>35</v>
       </c>
       <c r="W2" t="s" s="4">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="X2" t="s" s="2">
         <v>38</v>
@@ -452,37 +458,37 @@
       <c r="Y2" t="s" s="5">
         <v>39</v>
       </c>
-      <c r="Z2" t="s" s="1">
-        <v>35</v>
-      </c>
-      <c r="AA2" t="s" s="4">
-        <v>37</v>
-      </c>
-      <c r="AB2" t="s" s="1">
-        <v>35</v>
-      </c>
-      <c r="AC2" t="s" s="4">
-        <v>37</v>
-      </c>
-      <c r="AD2" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="AE2" t="s" s="5">
-        <v>39</v>
+      <c r="Z2" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AA2" t="s" s="5">
+        <v>39</v>
+      </c>
+      <c r="AB2" t="s" s="4">
+        <v>40</v>
+      </c>
+      <c r="AC2" t="s" s="1">
+        <v>35</v>
+      </c>
+      <c r="AD2" t="s" s="4">
+        <v>40</v>
+      </c>
+      <c r="AE2" t="s" s="1">
+        <v>35</v>
       </c>
       <c r="AF2" t="s" s="4">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="AG2" t="s" s="0">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AH2" t="s" s="0">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B3" t="s" s="1">
         <v>35</v>
@@ -490,65 +496,65 @@
       <c r="C3" t="s" s="6">
         <v>36</v>
       </c>
-      <c r="D3" t="s" s="1">
-        <v>35</v>
-      </c>
-      <c r="E3" t="s" s="4">
+      <c r="D3" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="E3" t="s" s="5">
+        <v>39</v>
+      </c>
+      <c r="F3" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="G3" t="s" s="5">
+        <v>39</v>
+      </c>
+      <c r="H3" t="s" s="3">
         <v>37</v>
       </c>
-      <c r="F3" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="G3" t="s" s="5">
-        <v>39</v>
-      </c>
-      <c r="H3" t="s" s="1">
-        <v>35</v>
-      </c>
-      <c r="I3" t="s" s="4">
-        <v>37</v>
-      </c>
-      <c r="J3" t="s" s="1">
-        <v>35</v>
-      </c>
-      <c r="K3" t="s" s="4">
-        <v>37</v>
-      </c>
-      <c r="L3" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="M3" t="s" s="5">
-        <v>39</v>
-      </c>
-      <c r="N3" t="s" s="1">
-        <v>35</v>
-      </c>
-      <c r="O3" t="s" s="4">
-        <v>37</v>
-      </c>
-      <c r="P3" t="s" s="1">
-        <v>35</v>
+      <c r="I3" t="s" s="1">
+        <v>35</v>
+      </c>
+      <c r="J3" t="s" s="4">
+        <v>40</v>
+      </c>
+      <c r="K3" t="s" s="1">
+        <v>35</v>
+      </c>
+      <c r="L3" t="s" s="4">
+        <v>40</v>
+      </c>
+      <c r="M3" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="N3" t="s" s="5">
+        <v>39</v>
+      </c>
+      <c r="O3" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="P3" t="s" s="5">
+        <v>39</v>
       </c>
       <c r="Q3" t="s" s="4">
-        <v>37</v>
-      </c>
-      <c r="R3" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="S3" t="s" s="5">
-        <v>39</v>
+        <v>40</v>
+      </c>
+      <c r="R3" t="s" s="1">
+        <v>35</v>
+      </c>
+      <c r="S3" t="s" s="4">
+        <v>40</v>
       </c>
       <c r="T3" t="s" s="1">
         <v>35</v>
       </c>
       <c r="U3" t="s" s="4">
-        <v>37</v>
-      </c>
-      <c r="V3" t="s" s="1">
-        <v>35</v>
-      </c>
-      <c r="W3" t="s" s="4">
-        <v>37</v>
+        <v>40</v>
+      </c>
+      <c r="V3" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="W3" t="s" s="5">
+        <v>39</v>
       </c>
       <c r="X3" t="s" s="2">
         <v>38</v>
@@ -556,37 +562,37 @@
       <c r="Y3" t="s" s="5">
         <v>39</v>
       </c>
-      <c r="Z3" t="s" s="1">
-        <v>35</v>
-      </c>
-      <c r="AA3" t="s" s="4">
-        <v>37</v>
-      </c>
-      <c r="AB3" t="s" s="1">
-        <v>35</v>
-      </c>
-      <c r="AC3" t="s" s="4">
-        <v>37</v>
-      </c>
-      <c r="AD3" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="AE3" t="s" s="5">
-        <v>39</v>
-      </c>
-      <c r="AF3" t="s" s="4">
-        <v>37</v>
+      <c r="Z3" t="s" s="4">
+        <v>40</v>
+      </c>
+      <c r="AA3" t="s" s="1">
+        <v>35</v>
+      </c>
+      <c r="AB3" t="s" s="4">
+        <v>40</v>
+      </c>
+      <c r="AC3" t="s" s="1">
+        <v>35</v>
+      </c>
+      <c r="AD3" t="s" s="4">
+        <v>40</v>
+      </c>
+      <c r="AE3" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AF3" t="s" s="5">
+        <v>39</v>
       </c>
       <c r="AG3" t="s" s="0">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AH3" t="s" s="0">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B4" t="s" s="2">
         <v>38</v>
@@ -600,47 +606,47 @@
       <c r="E4" t="s" s="5">
         <v>39</v>
       </c>
-      <c r="F4" t="s" s="1">
-        <v>35</v>
-      </c>
-      <c r="G4" t="s" s="6">
+      <c r="F4" t="s" s="6">
         <v>36</v>
       </c>
-      <c r="H4" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="I4" t="s" s="5">
-        <v>39</v>
-      </c>
-      <c r="J4" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="K4" t="s" s="5">
-        <v>39</v>
-      </c>
-      <c r="L4" t="s" s="1">
-        <v>35</v>
-      </c>
-      <c r="M4" t="s" s="4">
+      <c r="G4" t="s" s="1">
+        <v>35</v>
+      </c>
+      <c r="H4" t="s" s="3">
         <v>37</v>
       </c>
-      <c r="N4" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="O4" t="s" s="5">
-        <v>39</v>
-      </c>
-      <c r="P4" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="Q4" t="s" s="5">
-        <v>39</v>
+      <c r="I4" t="s" s="1">
+        <v>35</v>
+      </c>
+      <c r="J4" t="s" s="4">
+        <v>40</v>
+      </c>
+      <c r="K4" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="L4" t="s" s="5">
+        <v>39</v>
+      </c>
+      <c r="M4" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="N4" t="s" s="5">
+        <v>39</v>
+      </c>
+      <c r="O4" t="s" s="4">
+        <v>40</v>
+      </c>
+      <c r="P4" t="s" s="1">
+        <v>35</v>
+      </c>
+      <c r="Q4" t="s" s="4">
+        <v>40</v>
       </c>
       <c r="R4" t="s" s="1">
         <v>35</v>
       </c>
       <c r="S4" t="s" s="4">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="T4" t="s" s="2">
         <v>38</v>
@@ -654,43 +660,43 @@
       <c r="W4" t="s" s="5">
         <v>39</v>
       </c>
-      <c r="X4" t="s" s="1">
-        <v>35</v>
-      </c>
-      <c r="Y4" t="s" s="4">
-        <v>37</v>
-      </c>
-      <c r="Z4" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="AA4" t="s" s="5">
-        <v>39</v>
-      </c>
-      <c r="AB4" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="AC4" t="s" s="5">
-        <v>39</v>
-      </c>
-      <c r="AD4" t="s" s="1">
-        <v>35</v>
-      </c>
-      <c r="AE4" t="s" s="4">
-        <v>37</v>
-      </c>
-      <c r="AF4" t="s" s="4">
-        <v>37</v>
+      <c r="X4" t="s" s="4">
+        <v>40</v>
+      </c>
+      <c r="Y4" t="s" s="1">
+        <v>35</v>
+      </c>
+      <c r="Z4" t="s" s="4">
+        <v>40</v>
+      </c>
+      <c r="AA4" t="s" s="1">
+        <v>35</v>
+      </c>
+      <c r="AB4" t="s" s="4">
+        <v>40</v>
+      </c>
+      <c r="AC4" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AD4" t="s" s="5">
+        <v>39</v>
+      </c>
+      <c r="AE4" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AF4" t="s" s="5">
+        <v>39</v>
       </c>
       <c r="AG4" t="s" s="0">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AH4" t="s" s="0">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B5" t="s" s="2">
         <v>38</v>
@@ -698,53 +704,53 @@
       <c r="C5" t="s" s="5">
         <v>39</v>
       </c>
-      <c r="D5" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="E5" t="s" s="5">
-        <v>39</v>
-      </c>
-      <c r="F5" t="s" s="1">
-        <v>35</v>
-      </c>
-      <c r="G5" t="s" s="6">
+      <c r="D5" t="s" s="6">
         <v>36</v>
       </c>
-      <c r="H5" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="I5" t="s" s="5">
-        <v>39</v>
-      </c>
-      <c r="J5" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="K5" t="s" s="5">
-        <v>39</v>
-      </c>
-      <c r="L5" t="s" s="1">
-        <v>35</v>
+      <c r="E5" t="s" s="1">
+        <v>35</v>
+      </c>
+      <c r="F5" t="s" s="3">
+        <v>37</v>
+      </c>
+      <c r="G5" t="s" s="1">
+        <v>35</v>
+      </c>
+      <c r="H5" t="s" s="4">
+        <v>40</v>
+      </c>
+      <c r="I5" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="J5" t="s" s="5">
+        <v>39</v>
+      </c>
+      <c r="K5" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="L5" t="s" s="5">
+        <v>39</v>
       </c>
       <c r="M5" t="s" s="4">
-        <v>37</v>
-      </c>
-      <c r="N5" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="O5" t="s" s="5">
-        <v>39</v>
-      </c>
-      <c r="P5" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="Q5" t="s" s="5">
-        <v>39</v>
-      </c>
-      <c r="R5" t="s" s="1">
-        <v>35</v>
-      </c>
-      <c r="S5" t="s" s="4">
-        <v>37</v>
+        <v>40</v>
+      </c>
+      <c r="N5" t="s" s="1">
+        <v>35</v>
+      </c>
+      <c r="O5" t="s" s="4">
+        <v>40</v>
+      </c>
+      <c r="P5" t="s" s="1">
+        <v>35</v>
+      </c>
+      <c r="Q5" t="s" s="4">
+        <v>40</v>
+      </c>
+      <c r="R5" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="S5" t="s" s="5">
+        <v>39</v>
       </c>
       <c r="T5" t="s" s="2">
         <v>38</v>
@@ -752,49 +758,49 @@
       <c r="U5" t="s" s="5">
         <v>39</v>
       </c>
-      <c r="V5" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="W5" t="s" s="5">
-        <v>39</v>
-      </c>
-      <c r="X5" t="s" s="1">
-        <v>35</v>
-      </c>
-      <c r="Y5" t="s" s="4">
-        <v>37</v>
-      </c>
-      <c r="Z5" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="AA5" t="s" s="5">
-        <v>39</v>
-      </c>
-      <c r="AB5" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="AC5" t="s" s="5">
-        <v>39</v>
-      </c>
-      <c r="AD5" t="s" s="1">
-        <v>35</v>
+      <c r="V5" t="s" s="4">
+        <v>40</v>
+      </c>
+      <c r="W5" t="s" s="1">
+        <v>35</v>
+      </c>
+      <c r="X5" t="s" s="4">
+        <v>40</v>
+      </c>
+      <c r="Y5" t="s" s="1">
+        <v>35</v>
+      </c>
+      <c r="Z5" t="s" s="4">
+        <v>40</v>
+      </c>
+      <c r="AA5" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AB5" t="s" s="5">
+        <v>39</v>
+      </c>
+      <c r="AC5" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AD5" t="s" s="5">
+        <v>39</v>
       </c>
       <c r="AE5" t="s" s="4">
-        <v>37</v>
-      </c>
-      <c r="AF5" t="s" s="4">
-        <v>37</v>
+        <v>40</v>
+      </c>
+      <c r="AF5" t="s" s="1">
+        <v>35</v>
       </c>
       <c r="AG5" t="s" s="0">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AH5" t="s" s="0">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B6" t="s" s="6">
         <v>36</v>
@@ -802,14 +808,14 @@
       <c r="C6" t="s" s="1">
         <v>35</v>
       </c>
-      <c r="D6" t="s" s="4">
+      <c r="D6" t="s" s="3">
         <v>37</v>
       </c>
       <c r="E6" t="s" s="1">
         <v>35</v>
       </c>
       <c r="F6" t="s" s="4">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="G6" t="s" s="2">
         <v>38</v>
@@ -817,53 +823,53 @@
       <c r="H6" t="s" s="5">
         <v>39</v>
       </c>
-      <c r="I6" t="s" s="1">
-        <v>35</v>
-      </c>
-      <c r="J6" t="s" s="4">
-        <v>37</v>
-      </c>
-      <c r="K6" t="s" s="1">
-        <v>35</v>
-      </c>
-      <c r="L6" t="s" s="4">
-        <v>37</v>
-      </c>
-      <c r="M6" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="N6" t="s" s="5">
-        <v>39</v>
-      </c>
-      <c r="O6" t="s" s="1">
-        <v>35</v>
-      </c>
-      <c r="P6" t="s" s="4">
-        <v>37</v>
-      </c>
-      <c r="Q6" t="s" s="1">
-        <v>35</v>
-      </c>
-      <c r="R6" t="s" s="4">
-        <v>37</v>
-      </c>
-      <c r="S6" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="T6" t="s" s="5">
-        <v>39</v>
+      <c r="I6" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="J6" t="s" s="5">
+        <v>39</v>
+      </c>
+      <c r="K6" t="s" s="4">
+        <v>40</v>
+      </c>
+      <c r="L6" t="s" s="1">
+        <v>35</v>
+      </c>
+      <c r="M6" t="s" s="4">
+        <v>40</v>
+      </c>
+      <c r="N6" t="s" s="1">
+        <v>35</v>
+      </c>
+      <c r="O6" t="s" s="4">
+        <v>40</v>
+      </c>
+      <c r="P6" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="Q6" t="s" s="5">
+        <v>39</v>
+      </c>
+      <c r="R6" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="S6" t="s" s="5">
+        <v>39</v>
+      </c>
+      <c r="T6" t="s" s="4">
+        <v>40</v>
       </c>
       <c r="U6" t="s" s="1">
         <v>35</v>
       </c>
       <c r="V6" t="s" s="4">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="W6" t="s" s="1">
         <v>35</v>
       </c>
       <c r="X6" t="s" s="4">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="Y6" t="s" s="2">
         <v>38</v>
@@ -871,34 +877,34 @@
       <c r="Z6" t="s" s="5">
         <v>39</v>
       </c>
-      <c r="AA6" t="s" s="1">
-        <v>35</v>
-      </c>
-      <c r="AB6" t="s" s="4">
-        <v>37</v>
-      </c>
-      <c r="AC6" t="s" s="1">
-        <v>35</v>
-      </c>
-      <c r="AD6" t="s" s="4">
-        <v>37</v>
-      </c>
-      <c r="AE6" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="AF6" t="s" s="5">
-        <v>39</v>
+      <c r="AA6" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AB6" t="s" s="5">
+        <v>39</v>
+      </c>
+      <c r="AC6" t="s" s="4">
+        <v>40</v>
+      </c>
+      <c r="AD6" t="s" s="1">
+        <v>35</v>
+      </c>
+      <c r="AE6" t="s" s="4">
+        <v>40</v>
+      </c>
+      <c r="AF6" t="s" s="1">
+        <v>35</v>
       </c>
       <c r="AG6" t="s" s="0">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AH6" t="s" s="0">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="0">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B7" t="s" s="6">
         <v>36</v>
@@ -906,14 +912,14 @@
       <c r="C7" t="s" s="1">
         <v>35</v>
       </c>
-      <c r="D7" t="s" s="4">
+      <c r="D7" t="s" s="3">
         <v>37</v>
       </c>
-      <c r="E7" t="s" s="1">
-        <v>35</v>
-      </c>
-      <c r="F7" t="s" s="4">
-        <v>37</v>
+      <c r="E7" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="F7" t="s" s="5">
+        <v>39</v>
       </c>
       <c r="G7" t="s" s="2">
         <v>38</v>
@@ -921,53 +927,53 @@
       <c r="H7" t="s" s="5">
         <v>39</v>
       </c>
-      <c r="I7" t="s" s="1">
-        <v>35</v>
-      </c>
-      <c r="J7" t="s" s="4">
-        <v>37</v>
-      </c>
-      <c r="K7" t="s" s="1">
-        <v>35</v>
-      </c>
-      <c r="L7" t="s" s="4">
-        <v>37</v>
-      </c>
-      <c r="M7" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="N7" t="s" s="5">
-        <v>39</v>
-      </c>
-      <c r="O7" t="s" s="1">
-        <v>35</v>
-      </c>
-      <c r="P7" t="s" s="4">
-        <v>37</v>
-      </c>
-      <c r="Q7" t="s" s="1">
-        <v>35</v>
+      <c r="I7" t="s" s="4">
+        <v>40</v>
+      </c>
+      <c r="J7" t="s" s="1">
+        <v>35</v>
+      </c>
+      <c r="K7" t="s" s="4">
+        <v>40</v>
+      </c>
+      <c r="L7" t="s" s="1">
+        <v>35</v>
+      </c>
+      <c r="M7" t="s" s="4">
+        <v>40</v>
+      </c>
+      <c r="N7" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="O7" t="s" s="5">
+        <v>39</v>
+      </c>
+      <c r="P7" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="Q7" t="s" s="5">
+        <v>39</v>
       </c>
       <c r="R7" t="s" s="4">
-        <v>37</v>
-      </c>
-      <c r="S7" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="T7" t="s" s="5">
-        <v>39</v>
+        <v>40</v>
+      </c>
+      <c r="S7" t="s" s="1">
+        <v>35</v>
+      </c>
+      <c r="T7" t="s" s="4">
+        <v>40</v>
       </c>
       <c r="U7" t="s" s="1">
         <v>35</v>
       </c>
       <c r="V7" t="s" s="4">
-        <v>37</v>
-      </c>
-      <c r="W7" t="s" s="1">
-        <v>35</v>
-      </c>
-      <c r="X7" t="s" s="4">
-        <v>37</v>
+        <v>40</v>
+      </c>
+      <c r="W7" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="X7" t="s" s="5">
+        <v>39</v>
       </c>
       <c r="Y7" t="s" s="2">
         <v>38</v>
@@ -975,34 +981,34 @@
       <c r="Z7" t="s" s="5">
         <v>39</v>
       </c>
-      <c r="AA7" t="s" s="1">
-        <v>35</v>
-      </c>
-      <c r="AB7" t="s" s="4">
-        <v>37</v>
-      </c>
-      <c r="AC7" t="s" s="1">
-        <v>35</v>
-      </c>
-      <c r="AD7" t="s" s="4">
-        <v>37</v>
-      </c>
-      <c r="AE7" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="AF7" t="s" s="5">
-        <v>39</v>
+      <c r="AA7" t="s" s="4">
+        <v>40</v>
+      </c>
+      <c r="AB7" t="s" s="1">
+        <v>35</v>
+      </c>
+      <c r="AC7" t="s" s="4">
+        <v>40</v>
+      </c>
+      <c r="AD7" t="s" s="1">
+        <v>35</v>
+      </c>
+      <c r="AE7" t="s" s="4">
+        <v>40</v>
+      </c>
+      <c r="AF7" t="s" s="2">
+        <v>38</v>
       </c>
       <c r="AG7" t="s" s="0">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AH7" t="s" s="0">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="0">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B8" t="s" s="6">
         <v>36</v>
@@ -1019,47 +1025,47 @@
       <c r="F8" t="s" s="5">
         <v>39</v>
       </c>
-      <c r="G8" t="s" s="1">
-        <v>35</v>
-      </c>
-      <c r="H8" t="s" s="4">
+      <c r="G8" t="s" s="3">
         <v>37</v>
       </c>
-      <c r="I8" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="J8" t="s" s="5">
-        <v>39</v>
-      </c>
-      <c r="K8" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="L8" t="s" s="5">
-        <v>39</v>
-      </c>
-      <c r="M8" t="s" s="1">
-        <v>35</v>
-      </c>
-      <c r="N8" t="s" s="4">
-        <v>37</v>
-      </c>
-      <c r="O8" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="P8" t="s" s="5">
-        <v>39</v>
-      </c>
-      <c r="Q8" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="R8" t="s" s="5">
-        <v>39</v>
+      <c r="H8" t="s" s="1">
+        <v>35</v>
+      </c>
+      <c r="I8" t="s" s="4">
+        <v>40</v>
+      </c>
+      <c r="J8" t="s" s="1">
+        <v>35</v>
+      </c>
+      <c r="K8" t="s" s="4">
+        <v>40</v>
+      </c>
+      <c r="L8" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="M8" t="s" s="5">
+        <v>39</v>
+      </c>
+      <c r="N8" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="O8" t="s" s="5">
+        <v>39</v>
+      </c>
+      <c r="P8" t="s" s="4">
+        <v>40</v>
+      </c>
+      <c r="Q8" t="s" s="1">
+        <v>35</v>
+      </c>
+      <c r="R8" t="s" s="4">
+        <v>40</v>
       </c>
       <c r="S8" t="s" s="1">
         <v>35</v>
       </c>
       <c r="T8" t="s" s="4">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="U8" t="s" s="2">
         <v>38</v>
@@ -1073,40 +1079,40 @@
       <c r="X8" t="s" s="5">
         <v>39</v>
       </c>
-      <c r="Y8" t="s" s="1">
-        <v>35</v>
-      </c>
-      <c r="Z8" t="s" s="4">
-        <v>37</v>
-      </c>
-      <c r="AA8" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="AB8" t="s" s="5">
-        <v>39</v>
-      </c>
-      <c r="AC8" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="AD8" t="s" s="5">
-        <v>39</v>
-      </c>
-      <c r="AE8" t="s" s="1">
-        <v>35</v>
-      </c>
-      <c r="AF8" t="s" s="4">
-        <v>37</v>
+      <c r="Y8" t="s" s="4">
+        <v>40</v>
+      </c>
+      <c r="Z8" t="s" s="1">
+        <v>35</v>
+      </c>
+      <c r="AA8" t="s" s="4">
+        <v>40</v>
+      </c>
+      <c r="AB8" t="s" s="1">
+        <v>35</v>
+      </c>
+      <c r="AC8" t="s" s="4">
+        <v>40</v>
+      </c>
+      <c r="AD8" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AE8" t="s" s="5">
+        <v>39</v>
+      </c>
+      <c r="AF8" t="s" s="2">
+        <v>38</v>
       </c>
       <c r="AG8" t="s" s="0">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AH8" t="s" s="0">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="0">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B9" t="s" s="6">
         <v>36</v>
@@ -1117,95 +1123,199 @@
       <c r="D9" t="s" s="5">
         <v>39</v>
       </c>
-      <c r="E9" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="F9" t="s" s="5">
-        <v>39</v>
-      </c>
-      <c r="G9" t="s" s="1">
-        <v>35</v>
-      </c>
-      <c r="H9" t="s" s="4">
+      <c r="E9" t="s" s="3">
         <v>37</v>
       </c>
-      <c r="I9" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="J9" t="s" s="5">
-        <v>39</v>
-      </c>
-      <c r="K9" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="L9" t="s" s="5">
-        <v>39</v>
-      </c>
-      <c r="M9" t="s" s="1">
-        <v>35</v>
+      <c r="F9" t="s" s="1">
+        <v>35</v>
+      </c>
+      <c r="G9" t="s" s="3">
+        <v>37</v>
+      </c>
+      <c r="H9" t="s" s="1">
+        <v>35</v>
+      </c>
+      <c r="I9" t="s" s="4">
+        <v>40</v>
+      </c>
+      <c r="J9" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="K9" t="s" s="5">
+        <v>39</v>
+      </c>
+      <c r="L9" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="M9" t="s" s="5">
+        <v>39</v>
       </c>
       <c r="N9" t="s" s="4">
+        <v>40</v>
+      </c>
+      <c r="O9" t="s" s="1">
+        <v>35</v>
+      </c>
+      <c r="P9" t="s" s="4">
+        <v>40</v>
+      </c>
+      <c r="Q9" t="s" s="1">
+        <v>35</v>
+      </c>
+      <c r="R9" t="s" s="4">
+        <v>40</v>
+      </c>
+      <c r="S9" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="T9" t="s" s="5">
+        <v>39</v>
+      </c>
+      <c r="U9" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="V9" t="s" s="5">
+        <v>39</v>
+      </c>
+      <c r="W9" t="s" s="4">
+        <v>40</v>
+      </c>
+      <c r="X9" t="s" s="1">
+        <v>35</v>
+      </c>
+      <c r="Y9" t="s" s="4">
+        <v>40</v>
+      </c>
+      <c r="Z9" t="s" s="1">
+        <v>35</v>
+      </c>
+      <c r="AA9" t="s" s="4">
+        <v>40</v>
+      </c>
+      <c r="AB9" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AC9" t="s" s="5">
+        <v>39</v>
+      </c>
+      <c r="AD9" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AE9" t="s" s="5">
+        <v>39</v>
+      </c>
+      <c r="AF9" t="s" s="4">
+        <v>40</v>
+      </c>
+      <c r="AG9" t="s" s="0">
+        <v>41</v>
+      </c>
+      <c r="AH9" t="s" s="0">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s" s="0">
+        <v>50</v>
+      </c>
+      <c r="B10" t="s" s="6">
+        <v>36</v>
+      </c>
+      <c r="C10" t="s" s="3">
         <v>37</v>
       </c>
-      <c r="O9" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="P9" t="s" s="5">
-        <v>39</v>
-      </c>
-      <c r="Q9" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="R9" t="s" s="5">
-        <v>39</v>
-      </c>
-      <c r="S9" t="s" s="1">
-        <v>35</v>
-      </c>
-      <c r="T9" t="s" s="4">
+      <c r="D10" t="s" s="1">
+        <v>35</v>
+      </c>
+      <c r="E10" t="s" s="3">
         <v>37</v>
       </c>
-      <c r="U9" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="V9" t="s" s="5">
-        <v>39</v>
-      </c>
-      <c r="W9" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="X9" t="s" s="5">
-        <v>39</v>
-      </c>
-      <c r="Y9" t="s" s="1">
-        <v>35</v>
-      </c>
-      <c r="Z9" t="s" s="4">
-        <v>37</v>
-      </c>
-      <c r="AA9" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="AB9" t="s" s="5">
-        <v>39</v>
-      </c>
-      <c r="AC9" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="AD9" t="s" s="5">
-        <v>39</v>
-      </c>
-      <c r="AE9" t="s" s="1">
-        <v>35</v>
-      </c>
-      <c r="AF9" t="s" s="4">
-        <v>37</v>
-      </c>
-      <c r="AG9" t="s" s="0">
-        <v>40</v>
-      </c>
-      <c r="AH9" t="s" s="0">
+      <c r="F10" t="s" s="1">
+        <v>35</v>
+      </c>
+      <c r="G10" t="s" s="4">
+        <v>40</v>
+      </c>
+      <c r="H10" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="I10" t="s" s="5">
+        <v>39</v>
+      </c>
+      <c r="J10" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="K10" t="s" s="5">
+        <v>39</v>
+      </c>
+      <c r="L10" t="s" s="4">
+        <v>40</v>
+      </c>
+      <c r="M10" t="s" s="1">
+        <v>35</v>
+      </c>
+      <c r="N10" t="s" s="4">
+        <v>40</v>
+      </c>
+      <c r="O10" t="s" s="1">
+        <v>35</v>
+      </c>
+      <c r="P10" t="s" s="4">
+        <v>40</v>
+      </c>
+      <c r="Q10" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="R10" t="s" s="5">
+        <v>39</v>
+      </c>
+      <c r="S10" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="T10" t="s" s="5">
+        <v>39</v>
+      </c>
+      <c r="U10" t="s" s="4">
+        <v>40</v>
+      </c>
+      <c r="V10" t="s" s="1">
+        <v>35</v>
+      </c>
+      <c r="W10" t="s" s="4">
+        <v>40</v>
+      </c>
+      <c r="X10" t="s" s="1">
+        <v>35</v>
+      </c>
+      <c r="Y10" t="s" s="4">
+        <v>40</v>
+      </c>
+      <c r="Z10" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AA10" t="s" s="5">
+        <v>39</v>
+      </c>
+      <c r="AB10" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AC10" t="s" s="5">
+        <v>39</v>
+      </c>
+      <c r="AD10" t="s" s="4">
+        <v>40</v>
+      </c>
+      <c r="AE10" t="s" s="1">
+        <v>35</v>
+      </c>
+      <c r="AF10" t="s" s="4">
+        <v>40</v>
+      </c>
+      <c r="AG10" t="s" s="0">
         <v>41</v>
+      </c>
+      <c r="AH10" t="s" s="0">
+        <v>42</v>
       </c>
     </row>
   </sheetData>

--- a/sgturnos/mallas/malla_ter04_2026-01.xlsx
+++ b/sgturnos/mallas/malla_ter04_2026-01.xlsx
@@ -517,17 +517,17 @@
       <c r="J3" t="s" s="4">
         <v>40</v>
       </c>
-      <c r="K3" t="s" s="1">
-        <v>35</v>
-      </c>
-      <c r="L3" t="s" s="4">
-        <v>40</v>
-      </c>
-      <c r="M3" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="N3" t="s" s="5">
-        <v>39</v>
+      <c r="K3" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="L3" t="s" s="5">
+        <v>39</v>
+      </c>
+      <c r="M3" t="s" s="4">
+        <v>40</v>
+      </c>
+      <c r="N3" t="s" s="1">
+        <v>35</v>
       </c>
       <c r="O3" t="s" s="2">
         <v>38</v>
@@ -544,17 +544,17 @@
       <c r="S3" t="s" s="4">
         <v>40</v>
       </c>
-      <c r="T3" t="s" s="1">
-        <v>35</v>
-      </c>
-      <c r="U3" t="s" s="4">
-        <v>40</v>
-      </c>
-      <c r="V3" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="W3" t="s" s="5">
-        <v>39</v>
+      <c r="T3" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="U3" t="s" s="5">
+        <v>39</v>
+      </c>
+      <c r="V3" t="s" s="4">
+        <v>40</v>
+      </c>
+      <c r="W3" t="s" s="1">
+        <v>35</v>
       </c>
       <c r="X3" t="s" s="2">
         <v>38</v>
@@ -571,17 +571,17 @@
       <c r="AB3" t="s" s="4">
         <v>40</v>
       </c>
-      <c r="AC3" t="s" s="1">
-        <v>35</v>
-      </c>
-      <c r="AD3" t="s" s="4">
-        <v>40</v>
-      </c>
-      <c r="AE3" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="AF3" t="s" s="5">
-        <v>39</v>
+      <c r="AC3" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AD3" t="s" s="5">
+        <v>39</v>
+      </c>
+      <c r="AE3" t="s" s="4">
+        <v>40</v>
+      </c>
+      <c r="AF3" t="s" s="1">
+        <v>35</v>
       </c>
       <c r="AG3" t="s" s="0">
         <v>41</v>
@@ -600,32 +600,32 @@
       <c r="C4" t="s" s="5">
         <v>39</v>
       </c>
-      <c r="D4" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="E4" t="s" s="5">
-        <v>39</v>
-      </c>
-      <c r="F4" t="s" s="6">
+      <c r="D4" t="s" s="6">
         <v>36</v>
       </c>
+      <c r="E4" t="s" s="1">
+        <v>35</v>
+      </c>
+      <c r="F4" t="s" s="3">
+        <v>37</v>
+      </c>
       <c r="G4" t="s" s="1">
         <v>35</v>
       </c>
-      <c r="H4" t="s" s="3">
-        <v>37</v>
+      <c r="H4" t="s" s="4">
+        <v>40</v>
       </c>
       <c r="I4" t="s" s="1">
         <v>35</v>
       </c>
-      <c r="J4" t="s" s="4">
-        <v>40</v>
-      </c>
-      <c r="K4" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="L4" t="s" s="5">
-        <v>39</v>
+      <c r="J4" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="K4" t="s" s="5">
+        <v>39</v>
+      </c>
+      <c r="L4" t="s" s="4">
+        <v>40</v>
       </c>
       <c r="M4" t="s" s="2">
         <v>38</v>
@@ -645,14 +645,14 @@
       <c r="R4" t="s" s="1">
         <v>35</v>
       </c>
-      <c r="S4" t="s" s="4">
-        <v>40</v>
-      </c>
-      <c r="T4" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="U4" t="s" s="5">
-        <v>39</v>
+      <c r="S4" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="T4" t="s" s="5">
+        <v>39</v>
+      </c>
+      <c r="U4" t="s" s="4">
+        <v>40</v>
       </c>
       <c r="V4" t="s" s="2">
         <v>38</v>
@@ -672,14 +672,14 @@
       <c r="AA4" t="s" s="1">
         <v>35</v>
       </c>
-      <c r="AB4" t="s" s="4">
-        <v>40</v>
-      </c>
-      <c r="AC4" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="AD4" t="s" s="5">
-        <v>39</v>
+      <c r="AB4" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AC4" t="s" s="5">
+        <v>39</v>
+      </c>
+      <c r="AD4" t="s" s="4">
+        <v>40</v>
       </c>
       <c r="AE4" t="s" s="2">
         <v>38</v>
@@ -808,26 +808,26 @@
       <c r="C6" t="s" s="1">
         <v>35</v>
       </c>
-      <c r="D6" t="s" s="3">
+      <c r="D6" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="E6" t="s" s="5">
+        <v>39</v>
+      </c>
+      <c r="F6" t="s" s="3">
         <v>37</v>
       </c>
-      <c r="E6" t="s" s="1">
-        <v>35</v>
-      </c>
-      <c r="F6" t="s" s="4">
-        <v>40</v>
-      </c>
       <c r="G6" t="s" s="2">
         <v>38</v>
       </c>
       <c r="H6" t="s" s="5">
         <v>39</v>
       </c>
-      <c r="I6" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="J6" t="s" s="5">
-        <v>39</v>
+      <c r="I6" t="s" s="4">
+        <v>40</v>
+      </c>
+      <c r="J6" t="s" s="1">
+        <v>35</v>
       </c>
       <c r="K6" t="s" s="4">
         <v>40</v>
@@ -835,11 +835,11 @@
       <c r="L6" t="s" s="1">
         <v>35</v>
       </c>
-      <c r="M6" t="s" s="4">
-        <v>40</v>
-      </c>
-      <c r="N6" t="s" s="1">
-        <v>35</v>
+      <c r="M6" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="N6" t="s" s="5">
+        <v>39</v>
       </c>
       <c r="O6" t="s" s="4">
         <v>40</v>
@@ -850,11 +850,11 @@
       <c r="Q6" t="s" s="5">
         <v>39</v>
       </c>
-      <c r="R6" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="S6" t="s" s="5">
-        <v>39</v>
+      <c r="R6" t="s" s="4">
+        <v>40</v>
+      </c>
+      <c r="S6" t="s" s="1">
+        <v>35</v>
       </c>
       <c r="T6" t="s" s="4">
         <v>40</v>
@@ -862,11 +862,11 @@
       <c r="U6" t="s" s="1">
         <v>35</v>
       </c>
-      <c r="V6" t="s" s="4">
-        <v>40</v>
-      </c>
-      <c r="W6" t="s" s="1">
-        <v>35</v>
+      <c r="V6" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="W6" t="s" s="5">
+        <v>39</v>
       </c>
       <c r="X6" t="s" s="4">
         <v>40</v>
@@ -877,11 +877,11 @@
       <c r="Z6" t="s" s="5">
         <v>39</v>
       </c>
-      <c r="AA6" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="AB6" t="s" s="5">
-        <v>39</v>
+      <c r="AA6" t="s" s="4">
+        <v>40</v>
+      </c>
+      <c r="AB6" t="s" s="1">
+        <v>35</v>
       </c>
       <c r="AC6" t="s" s="4">
         <v>40</v>
@@ -889,11 +889,11 @@
       <c r="AD6" t="s" s="1">
         <v>35</v>
       </c>
-      <c r="AE6" t="s" s="4">
-        <v>40</v>
-      </c>
-      <c r="AF6" t="s" s="1">
-        <v>35</v>
+      <c r="AE6" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AF6" t="s" s="5">
+        <v>39</v>
       </c>
       <c r="AG6" t="s" s="0">
         <v>41</v>
@@ -1019,11 +1019,11 @@
       <c r="D8" t="s" s="5">
         <v>39</v>
       </c>
-      <c r="E8" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="F8" t="s" s="5">
-        <v>39</v>
+      <c r="E8" t="s" s="3">
+        <v>37</v>
+      </c>
+      <c r="F8" t="s" s="1">
+        <v>35</v>
       </c>
       <c r="G8" t="s" s="3">
         <v>37</v>
@@ -1031,11 +1031,11 @@
       <c r="H8" t="s" s="1">
         <v>35</v>
       </c>
-      <c r="I8" t="s" s="4">
-        <v>40</v>
-      </c>
-      <c r="J8" t="s" s="1">
-        <v>35</v>
+      <c r="I8" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="J8" t="s" s="5">
+        <v>39</v>
       </c>
       <c r="K8" t="s" s="4">
         <v>40</v>
@@ -1046,11 +1046,11 @@
       <c r="M8" t="s" s="5">
         <v>39</v>
       </c>
-      <c r="N8" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="O8" t="s" s="5">
-        <v>39</v>
+      <c r="N8" t="s" s="4">
+        <v>40</v>
+      </c>
+      <c r="O8" t="s" s="1">
+        <v>35</v>
       </c>
       <c r="P8" t="s" s="4">
         <v>40</v>
@@ -1058,11 +1058,11 @@
       <c r="Q8" t="s" s="1">
         <v>35</v>
       </c>
-      <c r="R8" t="s" s="4">
-        <v>40</v>
-      </c>
-      <c r="S8" t="s" s="1">
-        <v>35</v>
+      <c r="R8" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="S8" t="s" s="5">
+        <v>39</v>
       </c>
       <c r="T8" t="s" s="4">
         <v>40</v>
@@ -1073,11 +1073,11 @@
       <c r="V8" t="s" s="5">
         <v>39</v>
       </c>
-      <c r="W8" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="X8" t="s" s="5">
-        <v>39</v>
+      <c r="W8" t="s" s="4">
+        <v>40</v>
+      </c>
+      <c r="X8" t="s" s="1">
+        <v>35</v>
       </c>
       <c r="Y8" t="s" s="4">
         <v>40</v>
@@ -1085,11 +1085,11 @@
       <c r="Z8" t="s" s="1">
         <v>35</v>
       </c>
-      <c r="AA8" t="s" s="4">
-        <v>40</v>
-      </c>
-      <c r="AB8" t="s" s="1">
-        <v>35</v>
+      <c r="AA8" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AB8" t="s" s="5">
+        <v>39</v>
       </c>
       <c r="AC8" t="s" s="4">
         <v>40</v>
@@ -1100,8 +1100,8 @@
       <c r="AE8" t="s" s="5">
         <v>39</v>
       </c>
-      <c r="AF8" t="s" s="2">
-        <v>38</v>
+      <c r="AF8" t="s" s="4">
+        <v>40</v>
       </c>
       <c r="AG8" t="s" s="0">
         <v>41</v>
@@ -1227,11 +1227,11 @@
       <c r="D10" t="s" s="1">
         <v>35</v>
       </c>
-      <c r="E10" t="s" s="3">
-        <v>37</v>
-      </c>
-      <c r="F10" t="s" s="1">
-        <v>35</v>
+      <c r="E10" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="F10" t="s" s="5">
+        <v>39</v>
       </c>
       <c r="G10" t="s" s="4">
         <v>40</v>
@@ -1242,11 +1242,11 @@
       <c r="I10" t="s" s="5">
         <v>39</v>
       </c>
-      <c r="J10" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="K10" t="s" s="5">
-        <v>39</v>
+      <c r="J10" t="s" s="4">
+        <v>40</v>
+      </c>
+      <c r="K10" t="s" s="1">
+        <v>35</v>
       </c>
       <c r="L10" t="s" s="4">
         <v>40</v>
@@ -1254,11 +1254,11 @@
       <c r="M10" t="s" s="1">
         <v>35</v>
       </c>
-      <c r="N10" t="s" s="4">
-        <v>40</v>
-      </c>
-      <c r="O10" t="s" s="1">
-        <v>35</v>
+      <c r="N10" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="O10" t="s" s="5">
+        <v>39</v>
       </c>
       <c r="P10" t="s" s="4">
         <v>40</v>
@@ -1269,11 +1269,11 @@
       <c r="R10" t="s" s="5">
         <v>39</v>
       </c>
-      <c r="S10" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="T10" t="s" s="5">
-        <v>39</v>
+      <c r="S10" t="s" s="4">
+        <v>40</v>
+      </c>
+      <c r="T10" t="s" s="1">
+        <v>35</v>
       </c>
       <c r="U10" t="s" s="4">
         <v>40</v>
@@ -1281,11 +1281,11 @@
       <c r="V10" t="s" s="1">
         <v>35</v>
       </c>
-      <c r="W10" t="s" s="4">
-        <v>40</v>
-      </c>
-      <c r="X10" t="s" s="1">
-        <v>35</v>
+      <c r="W10" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="X10" t="s" s="5">
+        <v>39</v>
       </c>
       <c r="Y10" t="s" s="4">
         <v>40</v>
@@ -1296,11 +1296,11 @@
       <c r="AA10" t="s" s="5">
         <v>39</v>
       </c>
-      <c r="AB10" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="AC10" t="s" s="5">
-        <v>39</v>
+      <c r="AB10" t="s" s="4">
+        <v>40</v>
+      </c>
+      <c r="AC10" t="s" s="1">
+        <v>35</v>
       </c>
       <c r="AD10" t="s" s="4">
         <v>40</v>
@@ -1308,8 +1308,8 @@
       <c r="AE10" t="s" s="1">
         <v>35</v>
       </c>
-      <c r="AF10" t="s" s="4">
-        <v>40</v>
+      <c r="AF10" t="s" s="2">
+        <v>38</v>
       </c>
       <c r="AG10" t="s" s="0">
         <v>41</v>
